--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -705,17 +705,17 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-10 03:51:25</t>
+          <t>2025-09-10 21:39:55</t>
         </is>
       </c>
     </row>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -702,20 +702,20 @@
         </is>
       </c>
       <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
         <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-10 21:39:55</t>
+          <t>2025-09-10 22:25:58</t>
         </is>
       </c>
     </row>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -702,20 +702,20 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-10 22:25:58</t>
+          <t>2025-09-10 23:24:13</t>
         </is>
       </c>
     </row>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -125,9 +125,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:Y4" headerRowCount="1">
-  <autoFilter ref="A1:Y4"/>
-  <tableColumns count="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:T5" headerRowCount="1">
+  <autoFilter ref="A1:T5"/>
+  <tableColumns count="20">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
     <tableColumn id="3" name="Contact_Name"/>
@@ -148,11 +148,6 @@
     <tableColumn id="18" name="Active"/>
     <tableColumn id="19" name="Created_Date"/>
     <tableColumn id="20" name="Last_Modified"/>
-    <tableColumn id="21" name="Submitted_Count"/>
-    <tableColumn id="22" name="Pending_Count"/>
-    <tableColumn id="23" name="Pending_Approvals"/>
-    <tableColumn id="24" name="Completion_Rate"/>
-    <tableColumn id="25" name="Last_Updated"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -447,15 +442,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -470,11 +465,6 @@
     <col width="8" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,46 +568,21 @@
           <t>Last_Modified</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Submitted_Count</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Pending_Count</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Pending_Approvals</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Completion_Rate</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Last_Updated</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MGR_SUMMARY_M001_20250910</t>
+          <t>MGR_SUMMARY_M001_20250911</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sarah.johnson@attendo.com</t>
+          <t>alice.manager@attendo.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sarah Johnson</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -636,7 +601,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -665,7 +630,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Team Update: 4 team members need to submit their daily status</t>
+          <t>Team Update: 3 team members need to submit their daily status</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -673,9 +638,6 @@
           <t>team_m001</t>
         </is>
       </c>
-      <c r="O2" t="n">
-        <v/>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -693,46 +655,29 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-09-10 23:24:13</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MGR_SUMMARY_M002_20250910</t>
+          <t>MGR_SUMMARY_M002_20250911</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>michael.chen@attendo.com</t>
+          <t>bob.manager@attendo.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Michael Chen</t>
+          <t>Bob Chen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -751,7 +696,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -780,7 +725,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Team Update: 3 team members need to submit their daily status</t>
+          <t>Team Update: 1 team members need to submit their daily status</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -788,9 +733,6 @@
           <t>team_m002</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -808,44 +750,29 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
+          <t>2025-09-11 02:47:34</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MGR_SUMMARY_M003_20250910</t>
+          <t>MGR_SUMMARY_M003_20250911</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>emily.davis@attendo.com</t>
+          <t>carol.manager@attendo.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Emily Davis</t>
+          <t>Carol Davis</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -864,7 +791,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -893,7 +820,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Team Update: 3 team members need to submit their daily status</t>
+          <t>Team Update: 1 team members need to submit their daily status</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -901,9 +828,6 @@
           <t>team_m003</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -921,28 +845,108 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
+          <t>2025-09-11 02:47:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MGR_SUMMARY_MTK34710_20250911</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>chandresh.kerkar1@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chandresh</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MTK34710</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Team MTK34710</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TEAM_SUMMARY</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12:00,14:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Team Update: 1 team members need to submit their daily status</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>team_mtk34710</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2025-09-11 02:47:34</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:T5" headerRowCount="1">
-  <autoFilter ref="A1:T5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:T4" headerRowCount="1">
+  <autoFilter ref="A1:T4"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
@@ -442,15 +442,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -660,7 +660,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
@@ -850,102 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MGR_SUMMARY_MTK34710_20250911</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>chandresh.kerkar1@gmail.com</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chandresh</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MTK34710</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Team MTK34710</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>TEAM_SUMMARY</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>12:00,14:00</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Team Update: 1 team members need to submit their daily status</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>team_mtk34710</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -125,9 +125,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:T4" headerRowCount="1">
-  <autoFilter ref="A1:T4"/>
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:Y4" headerRowCount="1">
+  <autoFilter ref="A1:Y4"/>
+  <tableColumns count="25">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
     <tableColumn id="3" name="Contact_Name"/>
@@ -148,6 +148,11 @@
     <tableColumn id="18" name="Active"/>
     <tableColumn id="19" name="Created_Date"/>
     <tableColumn id="20" name="Last_Modified"/>
+    <tableColumn id="21" name="Submitted_Count"/>
+    <tableColumn id="22" name="Pending_Count"/>
+    <tableColumn id="23" name="Pending_Approvals"/>
+    <tableColumn id="24" name="Completion_Rate"/>
+    <tableColumn id="25" name="Last_Updated"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -442,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -465,6 +470,11 @@
     <col width="8" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,6 +578,31 @@
           <t>Last_Modified</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Submitted_Count</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Pending_Count</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Pending_Approvals</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Completion_Rate</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Last_Updated</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -638,6 +673,9 @@
           <t>team_m001</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v/>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -661,6 +699,23 @@
       <c r="T2" t="inlineStr">
         <is>
           <t>2025-09-11 22:16:31</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:27:33</t>
         </is>
       </c>
     </row>
@@ -733,6 +788,9 @@
           <t>team_m002</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -757,6 +815,21 @@
         <is>
           <t>2025-09-11 22:16:31</t>
         </is>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -828,6 +901,9 @@
           <t>team_m003</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -852,6 +928,21 @@
         <is>
           <t>2025-09-11 22:16:31</t>
         </is>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -125,9 +125,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:T4" headerRowCount="1">
-  <autoFilter ref="A1:T4"/>
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:Y4" headerRowCount="1">
+  <autoFilter ref="A1:Y4"/>
+  <tableColumns count="25">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
     <tableColumn id="3" name="Contact_Name"/>
@@ -148,6 +148,11 @@
     <tableColumn id="18" name="Active"/>
     <tableColumn id="19" name="Created_Date"/>
     <tableColumn id="20" name="Last_Modified"/>
+    <tableColumn id="21" name="Submitted_Count"/>
+    <tableColumn id="22" name="Pending_Count"/>
+    <tableColumn id="23" name="Pending_Approvals"/>
+    <tableColumn id="24" name="Completion_Rate"/>
+    <tableColumn id="25" name="Last_Updated"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -442,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -465,6 +470,11 @@
     <col width="8" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,6 +578,31 @@
           <t>Last_Modified</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Submitted_Count</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Pending_Count</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Pending_Approvals</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Completion_Rate</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Last_Updated</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -638,6 +673,9 @@
           <t>team_m001</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v/>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -661,6 +699,23 @@
       <c r="T2" t="inlineStr">
         <is>
           <t>2025-09-11 22:16:31</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-09-12 02:06:45</t>
         </is>
       </c>
     </row>
@@ -733,6 +788,9 @@
           <t>team_m002</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -757,6 +815,21 @@
         <is>
           <t>2025-09-11 22:16:31</t>
         </is>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -828,6 +901,9 @@
           <t>team_m003</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>EMAIL,TEAMS</t>
@@ -852,6 +928,21 @@
         <is>
           <t>2025-09-11 22:16:31</t>
         </is>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/notification_configs/02_manager_summary_notifications.xlsx
+++ b/notification_configs/02_manager_summary_notifications.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotificationData" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -125,36 +125,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManagerSummaryNotifications" displayName="ManagerSummaryNotifications" ref="A1:Y4" headerRowCount="1">
-  <autoFilter ref="A1:Y4"/>
-  <tableColumns count="25">
-    <tableColumn id="1" name="Primary_Key"/>
-    <tableColumn id="2" name="Contact_Email"/>
-    <tableColumn id="3" name="Contact_Name"/>
-    <tableColumn id="4" name="Manager_ID"/>
-    <tableColumn id="5" name="Department"/>
-    <tableColumn id="6" name="Team_Name"/>
-    <tableColumn id="7" name="Pending_Submissions"/>
-    <tableColumn id="8" name="Send_Notification"/>
-    <tableColumn id="9" name="Notification_Type"/>
-    <tableColumn id="10" name="Notification_Time"/>
-    <tableColumn id="11" name="Include_Vendor_List"/>
-    <tableColumn id="12" name="Escalation_Required"/>
-    <tableColumn id="13" name="Custom_Message"/>
-    <tableColumn id="14" name="Teams_Channel"/>
-    <tableColumn id="15" name="Phone_Number"/>
-    <tableColumn id="16" name="Notification_Method"/>
-    <tableColumn id="17" name="Priority"/>
-    <tableColumn id="18" name="Active"/>
-    <tableColumn id="19" name="Created_Date"/>
-    <tableColumn id="20" name="Last_Modified"/>
-    <tableColumn id="21" name="Submitted_Count"/>
-    <tableColumn id="22" name="Pending_Count"/>
-    <tableColumn id="23" name="Pending_Approvals"/>
-    <tableColumn id="24" name="Completion_Rate"/>
-    <tableColumn id="25" name="Last_Updated"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NotificationTable" displayName="NotificationTable" ref="A1:E7" headerRowCount="1">
+  <autoFilter ref="A1:E7"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="EmployeeID"/>
+    <tableColumn id="2" name="ContactEmail"/>
+    <tableColumn id="3" name="Message"/>
+    <tableColumn id="4" name="NotificationType"/>
+    <tableColumn id="5" name="Priority"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -447,502 +427,203 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Primary_Key</t>
+          <t>EmployeeID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Contact_Email</t>
+          <t>ContactEmail</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Contact_Name</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Manager_ID</t>
+          <t>NotificationType</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Team_Name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Pending_Submissions</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Send_Notification</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Notification_Type</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Notification_Time</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Include_Vendor_List</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Escalation_Required</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Custom_Message</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Teams_Channel</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Phone_Number</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Notification_Method</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
           <t>Priority</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Created_Date</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Last_Modified</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Submitted_Count</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Pending_Count</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Pending_Approvals</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Completion_Rate</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Last_Updated</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MGR_SUMMARY_M001_20250911</t>
+          <t>EMP001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>alice.manager@attendo.com</t>
+          <t>john.vendor@company.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>Team timesheet summary for review</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>Manager Summary</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Team M001</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TEAM_SUMMARY</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>12:00,14:00</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Team Update: 3 team members need to submit their daily status</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>team_m001</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v/>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2025-09-11 22:16:31</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-09-12 02:06:45</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MGR_SUMMARY_M002_20250911</t>
+          <t>EMP002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bob.manager@attendo.com</t>
+          <t>jane.vendor@company.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bob Chen</t>
+          <t>Weekly vendor timesheet report ready</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>Manager Summary</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Team M002</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TEAM_SUMMARY</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>12:00,14:00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Team Update: 1 team members need to submit their daily status</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>team_m002</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2025-09-11 22:16:31</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
+          <t>Medium</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MGR_SUMMARY_M003_20250911</t>
+          <t>EMP003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>carol.manager@attendo.com</t>
+          <t>mike.vendor@company.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Carol Davis</t>
+          <t>Please review team submissions</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>Manager Summary</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Team M003</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TEAM_SUMMARY</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>12:00,14:00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Team Update: 1 team members need to submit their daily status</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>team_m003</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2025-09-11 22:16:31</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sarah.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Team timesheet summary for review</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Manager Summary</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EMP005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>david.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Weekly vendor timesheet report ready</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Manager Summary</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test001@company.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Please review team submissions</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Manager Summary</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
     </row>
   </sheetData>
